--- a/example_data/data/Patient_list/patient_list.xlsx
+++ b/example_data/data/Patient_list/patient_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\SAM_echo_xjtlu\example_data\data\Patient_list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74BD7E9-BBCB-455D-BECC-C5B019F2CED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99EA6E1A-13AC-471D-8120-295790A9B21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2310" yWindow="6375" windowWidth="21600" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2310" yWindow="4335" windowWidth="21600" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,36 +25,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>patient_id</t>
   </si>
   <si>
-    <t>slice_index</t>
-  </si>
-  <si>
     <t>img_file</t>
   </si>
   <si>
     <t>seg_file</t>
   </si>
   <si>
-    <t>ID_0002</t>
-  </si>
-  <si>
     <t>batch</t>
   </si>
   <si>
-    <t>/host/d/Github/SAM_echo_xjtlu/example_data/data/ID_0002/img_slice00.nii.gz</t>
-  </si>
-  <si>
-    <t>/host/d/Github/SAM_echo_xjtlu/example_data/data/ID_0002/seg_slice00.nii.gz</t>
-  </si>
-  <si>
-    <t>/host/d/Github/SAM_echo_xjtlu/example_data/data/ID_0002/img_slice01.nii.gz</t>
-  </si>
-  <si>
-    <t>/host/d/Github/SAM_echo_xjtlu/example_data/data/ID_0002/seg_slice01.nii.gz</t>
+    <t>example_0001</t>
+  </si>
+  <si>
+    <t>example_0002</t>
+  </si>
+  <si>
+    <t>/host/d/Github/SAM_echo_xjtlu/example_data/data/example_0002/img.nii.gz</t>
+  </si>
+  <si>
+    <t>/host/d/Github/SAM_echo_xjtlu/example_data/data/example_0002/seg.nii.gz</t>
+  </si>
+  <si>
+    <t>/host/d/Github/SAM_echo_xjtlu/example_data/data/example_0001/img.nii.gz</t>
+  </si>
+  <si>
+    <t>/host/d/Github/SAM_echo_xjtlu/example_data/data/example_0001/seg.nii.gz</t>
   </si>
 </sst>
 </file>
@@ -417,12 +417,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -433,42 +436,33 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>0</v>
+      <c r="C2" t="s">
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
